--- a/artfynd/A 42309-2019 artfynd.xlsx
+++ b/artfynd/A 42309-2019 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>113237053</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2019 artfynd.xlsx
+++ b/artfynd/A 42309-2019 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>113237053</v>
       </c>
       <c r="B8" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2019 artfynd.xlsx
+++ b/artfynd/A 42309-2019 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>113237053</v>
       </c>
       <c r="B8" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2019 artfynd.xlsx
+++ b/artfynd/A 42309-2019 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>113237053</v>
       </c>
       <c r="B8" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2019 artfynd.xlsx
+++ b/artfynd/A 42309-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
